--- a/data/generated_mock_data/Coastal_Transmission_Partners.xlsx
+++ b/data/generated_mock_data/Coastal_Transmission_Partners.xlsx
@@ -521,40 +521,40 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>West Rincon Seam Intertie 230kV</t>
+          <t>Brunswick Seaport Reliability Line</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Faulkville Junction</t>
+          <t>Glynn Station</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>32.22</v>
+        <v>31.17</v>
       </c>
       <c r="G2" t="n">
-        <v>-81.33</v>
+        <v>-81.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Ebenezer Tap</t>
+          <t>St Simons Tap</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>32.24</v>
+        <v>31.19</v>
       </c>
       <c r="J2" t="n">
-        <v>-81.34999999999999</v>
+        <v>-81.52</v>
       </c>
       <c r="K2" t="n">
-        <v>32.23</v>
+        <v>31.18</v>
       </c>
       <c r="L2" t="n">
-        <v>-81.34</v>
+        <v>-81.51000000000001</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2027-01-15</t>
         </is>
       </c>
       <c r="N2" t="n">
